--- a/Result/profitability/6144.xlsx
+++ b/Result/profitability/6144.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.08</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.10625</v>
+        <v>-0.0625</v>
       </c>
       <c r="N2" t="n">
-        <v>36.83625</v>
+        <v>36.95874999999999</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.29</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.13875</v>
+        <v>-0.05875</v>
       </c>
       <c r="N3" t="n">
-        <v>34.49125</v>
+        <v>35.80875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.51</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1625</v>
+        <v>-0.1075</v>
       </c>
       <c r="N4" t="n">
-        <v>33.7175</v>
+        <v>33.9825</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.06</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.14</v>
+        <v>-0.08249999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>31.835</v>
+        <v>31.86</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.08</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1125</v>
+        <v>-0.06999999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>30.63375</v>
+        <v>30.66125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1149,7 +1149,7 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.27</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.14375</v>
+        <v>-0.09375</v>
       </c>
       <c r="N7" t="n">
-        <v>29.195</v>
+        <v>29.14125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.29875</v>
+        <v>-0.23125</v>
       </c>
       <c r="N8" t="n">
-        <v>27.6025</v>
+        <v>27.7175</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9820,6 +9820,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6144</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>38</v>
+      </c>
+      <c r="D75" t="n">
+        <v>22</v>
+      </c>
+      <c r="E75" t="n">
+        <v>15</v>
+      </c>
+      <c r="F75" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-19.14%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>19</v>
+      </c>
+      <c r="J75" t="n">
+        <v>12</v>
+      </c>
+      <c r="K75" t="n">
+        <v>12</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.07625000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>39.01125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-2.454545454545455</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.9200000000000017</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.0230518667000752</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.285714285714286</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.1999999999999957</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.004922471080482271</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
